--- a/output/4_lr_coefficients.xlsx
+++ b/output/4_lr_coefficients.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,14 +463,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Year_2012</t>
+          <t>Intercept</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.607588935018939</v>
+        <v>-1.775081239818172</v>
       </c>
       <c r="D2" t="n">
-        <v>1.607588935018939</v>
+        <v>1.775081239818172</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -486,18 +486,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Year_2011</t>
+          <t>AnnualIncome_Bin_4</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-1.110439651003149</v>
+        <v>0.9300814434327873</v>
       </c>
       <c r="D3" t="n">
-        <v>1.110439651003149</v>
+        <v>0.9300814434327873</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -509,18 +509,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>Credit_Bin_4</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-1.100911177135361</v>
+        <v>0.8560271199138917</v>
       </c>
       <c r="D4" t="n">
-        <v>1.100911177135361</v>
+        <v>0.8560271199138917</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -532,14 +532,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Credit_Bin_4</t>
+          <t>AnnualIncome_Bin_1</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.076591000950109</v>
+        <v>0.7349884656479132</v>
       </c>
       <c r="D5" t="n">
-        <v>1.076591000950109</v>
+        <v>0.7349884656479132</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -555,18 +555,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Age_Bin_4</t>
+          <t>AnnualIncome_Bin_3</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.991048415120599</v>
+        <v>0.6560499144357463</v>
       </c>
       <c r="D6" t="n">
-        <v>0.991048415120599</v>
+        <v>0.6560499144357463</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -578,18 +578,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AnnualIncome_Bin_1</t>
+          <t>Age_Bin_4</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8537974222158715</v>
+        <v>-0.6399456927812007</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8537974222158715</v>
+        <v>0.6399456927812007</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -601,14 +601,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Credit_Bin_2</t>
+          <t>MaritalStatus_Married</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.8518367374962826</v>
+        <v>0.6131973131870535</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8518367374962826</v>
+        <v>0.6131973131870535</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -624,18 +624,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Credit_Bin_3</t>
+          <t>ServiceType_H</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8051112284179315</v>
+        <v>-0.585358978500636</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8051112284179315</v>
+        <v>0.585358978500636</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -647,14 +647,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AnnualIncome_Bin_4</t>
+          <t>MaritalStatus_Single</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6927855161394159</v>
+        <v>0.558849545538056</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6927855161394159</v>
+        <v>0.558849545538056</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -670,18 +670,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ServiceType_H</t>
+          <t>Credit_Bin_3</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.5300906408847912</v>
+        <v>0.5429510722540634</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5300906408847912</v>
+        <v>0.5429510722540634</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -693,14 +693,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Year_2010</t>
+          <t>Dependents_Yes</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.4897583292983559</v>
+        <v>-0.5235391429046492</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4897583292983559</v>
+        <v>0.5235391429046492</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -716,18 +716,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Month_Bin_4</t>
+          <t>AnnualIncome_Bin_2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.4845923501105867</v>
+        <v>0.4214446091155656</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4845923501105867</v>
+        <v>0.4214446091155656</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -739,14 +739,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Credit_Bin_1</t>
+          <t>Credit_Bin_2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4701578737400577</v>
+        <v>0.3348762623295585</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4701578737400577</v>
+        <v>0.3348762623295585</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -762,18 +762,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Month_Bin_3</t>
+          <t>Classification1_4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.4433283602155409</v>
+        <v>0.327803794719082</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4433283602155409</v>
+        <v>0.327803794719082</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -785,14 +785,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ServiceType_E</t>
+          <t>Market_Northeast</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.3856623821054619</v>
+        <v>-0.3185361110113766</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3856623821054619</v>
+        <v>0.3185361110113766</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -808,18 +808,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AnnualIncome_Bin_3</t>
+          <t>NewCustomer_Y</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.3826086572671346</v>
+        <v>-0.306755104788021</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3826086572671346</v>
+        <v>0.306755104788021</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -831,18 +831,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ServiceType_N</t>
+          <t>Dependents_No</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.323136842190785</v>
+        <v>-0.3031128633851535</v>
       </c>
       <c r="D18" t="n">
-        <v>0.323136842190785</v>
+        <v>0.3031128633851535</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -854,18 +854,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ServiceType_I</t>
+          <t>Classification2_3</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.3220015780192595</v>
+        <v>0.2759592779239948</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3220015780192595</v>
+        <v>0.2759592779239948</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -877,18 +877,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NewCustomer_Y</t>
+          <t>PaymentMethod_Gov</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.3155528051776892</v>
+        <v>0.2665767057052663</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3155528051776892</v>
+        <v>0.2665767057052663</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -900,14 +900,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Month_Bin_2</t>
+          <t>ServiceType_I</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.2948650656996719</v>
+        <v>-0.2547904228041609</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2948650656996719</v>
+        <v>0.2547904228041609</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -923,18 +923,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Classification2_3</t>
+          <t>Market_Southeast</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.2784951677667805</v>
+        <v>-0.2503795067213828</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2784951677667805</v>
+        <v>0.2503795067213828</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -946,18 +946,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Market_Northeast</t>
+          <t>MaritalStatus_Separ</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.2716995140446866</v>
+        <v>0.2469220388623485</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2716995140446866</v>
+        <v>0.2469220388623485</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -969,14 +969,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Classification1_4</t>
+          <t>ServiceType_N</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.2684221771344804</v>
+        <v>0.2424711425159703</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2684221771344804</v>
+        <v>0.2424711425159703</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -992,14 +992,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MaritalStatus_Separ</t>
+          <t>Market_Southwest</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.2662949174351459</v>
+        <v>-0.2381187461178156</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2662949174351459</v>
+        <v>0.2381187461178156</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1015,14 +1015,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Market_Southeast</t>
+          <t>Age_Bin_1</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.2522603903869658</v>
+        <v>-0.2333034535633122</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2522603903869658</v>
+        <v>0.2333034535633122</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1038,18 +1038,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Government_Y</t>
+          <t>Market_Midwest</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.2498311381570798</v>
+        <v>-0.2140959655035181</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2498311381570798</v>
+        <v>0.2140959655035181</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1061,14 +1061,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ServiceType_M</t>
+          <t>Market_Internet</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.248402015449404</v>
+        <v>-0.2114122038929303</v>
       </c>
       <c r="D28" t="n">
-        <v>0.248402015449404</v>
+        <v>0.2114122038929303</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.2268256925911442</v>
+        <v>0.2019002781472106</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2268256925911442</v>
+        <v>0.2019002781472106</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1107,18 +1107,18 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Market_Southwest</t>
+          <t>Classification1_2</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.2249915422306578</v>
+        <v>0.1913824781176724</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2249915422306578</v>
+        <v>0.1913824781176724</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1130,14 +1130,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Age_Bin_1</t>
+          <t>ServiceType_M</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.2067859014463378</v>
+        <v>-0.1878740617797593</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2067859014463378</v>
+        <v>0.1878740617797593</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1153,18 +1153,18 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Market_Western</t>
+          <t>ServiceType_E</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.2062216381444697</v>
+        <v>-0.1875593916248588</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2062216381444697</v>
+        <v>0.1875593916248588</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1176,18 +1176,18 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AnnualIncome_Bin_2</t>
+          <t>Market_MountainPlains</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.2015009184414736</v>
+        <v>-0.1820910582567367</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2015009184414736</v>
+        <v>0.1820910582567367</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1199,18 +1199,18 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ServiceType_C</t>
+          <t>Classification1_3</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-0.1976182455797013</v>
+        <v>0.1737142952787211</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1976182455797013</v>
+        <v>0.1737142952787211</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1222,18 +1222,18 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Classification1_2</t>
+          <t>Age_Bin_2</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.1947244169010766</v>
+        <v>-0.1735698721067499</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1947244169010766</v>
+        <v>0.1735698721067499</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1245,14 +1245,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dependents_No</t>
+          <t>PaymentMethod_Other</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.1880349014488747</v>
+        <v>0.1428364623582263</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1880349014488747</v>
+        <v>0.1428364623582263</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1268,14 +1268,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PaymentMethod_Other</t>
+          <t>Classification2_1</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.1833486484273402</v>
+        <v>0.1346139903738221</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1833486484273402</v>
+        <v>0.1346139903738221</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1291,14 +1291,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Classification1_3</t>
+          <t>Classification2_2</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.1750249905677639</v>
+        <v>0.1341046846056608</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1750249905677639</v>
+        <v>0.1341046846056608</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1314,14 +1314,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Market_Internet</t>
+          <t>ServiceType_C</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-0.1730656938294464</v>
+        <v>-0.1175476269320489</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1730656938294464</v>
+        <v>0.1175476269320489</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1337,18 +1337,18 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Classification2_1</t>
+          <t>Credit_Bin_1</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.1699115797760999</v>
+        <v>-0.0933045185558813</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1699115797760999</v>
+        <v>0.0933045185558813</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.1564202980769208</v>
+        <v>-0.08953768574986209</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1564202980769208</v>
+        <v>0.08953768574986209</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1383,14 +1383,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Age_Bin_2</t>
+          <t>Age_Bin_3</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-0.1450909986514161</v>
+        <v>-0.08717209417143706</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1450909986514161</v>
+        <v>0.08717209417143706</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1406,18 +1406,18 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Classification2_2</t>
+          <t>Gender_M</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.1294722209816838</v>
+        <v>-0.08003371916667354</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1294722209816838</v>
+        <v>0.08003371916667354</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1429,18 +1429,18 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Month_Bin_1</t>
+          <t>Government_Y</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-0.1293258643301473</v>
+        <v>0.0671140822579981</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1293258643301473</v>
+        <v>0.0671140822579981</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1452,18 +1452,18 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Market_Midwest</t>
+          <t>Classification2_4</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.1252478842586283</v>
+        <v>0.04825337565820389</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1252478842586283</v>
+        <v>0.04825337565820389</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1475,18 +1475,18 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Age_Bin_3</t>
+          <t>Market_Western</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.1148680939571488</v>
+        <v>0.03965919505471247</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1148680939571488</v>
+        <v>0.03965919505471247</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1498,14 +1498,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gender_M</t>
+          <t>PaymentMethod_Direct</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.1009190873183679</v>
+        <v>-0.028099110560353</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1009190873183679</v>
+        <v>0.028099110560353</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1516,134 +1516,134 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>High Group</t>
+          <t>Low Group</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Classification2_4</t>
+          <t>Intercept</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.09191358712289406</v>
+        <v>-3.075578845403861</v>
       </c>
       <c r="D48" t="n">
-        <v>0.09191358712289406</v>
+        <v>3.075578845403861</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>High Group</t>
+          <t>Low Group</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PaymentMethod_Gov</t>
+          <t>ServiceType_E</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.07205584642549202</v>
+        <v>-1.652552486261437</v>
       </c>
       <c r="D49" t="n">
-        <v>0.07205584642549202</v>
+        <v>1.652552486261437</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>High Group</t>
+          <t>Low Group</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MaritalStatus_Single</t>
+          <t>AnnualIncome_Bin_4</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.06770635954847595</v>
+        <v>1.442366050569234</v>
       </c>
       <c r="D50" t="n">
-        <v>0.06770635954847595</v>
+        <v>1.442366050569234</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>High Group</t>
+          <t>Low Group</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Market_MountainPlains</t>
+          <t>AnnualIncome_Bin_3</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.06152751241994898</v>
+        <v>1.00944036696658</v>
       </c>
       <c r="D51" t="n">
-        <v>0.06152751241994898</v>
+        <v>1.00944036696658</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>High Group</t>
+          <t>Low Group</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PaymentMethod_Direct</t>
+          <t>ServiceType_H</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.04133525403493624</v>
+        <v>-0.77592618088068</v>
       </c>
       <c r="D52" t="n">
-        <v>0.04133525403493624</v>
+        <v>0.77592618088068</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>High Group</t>
+          <t>Low Group</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MaritalStatus_Married</t>
+          <t>AnnualIncome_Bin_2</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.02970080962796883</v>
+        <v>0.7093996904874622</v>
       </c>
       <c r="D53" t="n">
-        <v>0.02970080962796883</v>
+        <v>0.7093996904874622</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1654,19 +1654,19 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>High Group</t>
+          <t>Low Group</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dependents_Yes</t>
+          <t>MaritalStatus_Married</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4.304621943321957e-05</v>
+        <v>0.6895226394143202</v>
       </c>
       <c r="D54" t="n">
-        <v>4.304621943321957e-05</v>
+        <v>0.6895226394143202</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1682,18 +1682,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Year_2012</t>
+          <t>MaritalStatus_Single</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-1.904631634469578</v>
+        <v>0.6693071691001571</v>
       </c>
       <c r="D55" t="n">
-        <v>1.904631634469578</v>
+        <v>0.6693071691001571</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1705,14 +1705,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ServiceType_E</t>
+          <t>Dependents_Yes</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-1.727323691355894</v>
+        <v>-0.6555606956908567</v>
       </c>
       <c r="D56" t="n">
-        <v>1.727323691355894</v>
+        <v>0.6555606956908567</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1728,18 +1728,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Year_2011</t>
+          <t>Credit_Bin_4</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-1.634213978992889</v>
+        <v>0.6555372252229282</v>
       </c>
       <c r="D57" t="n">
-        <v>1.634213978992889</v>
+        <v>0.6555372252229282</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1751,14 +1751,14 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AnnualIncome_Bin_3</t>
+          <t>Age_Bin_3</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.341637396172191</v>
+        <v>0.5399813599871844</v>
       </c>
       <c r="D58" t="n">
-        <v>1.341637396172191</v>
+        <v>0.5399813599871844</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1774,14 +1774,14 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>Credit_Bin_1</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-1.150894546538485</v>
+        <v>-0.5303575156470306</v>
       </c>
       <c r="D59" t="n">
-        <v>1.150894546538485</v>
+        <v>0.5303575156470306</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1797,18 +1797,18 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Month_Bin_3</t>
+          <t>MaritalStatus_Separ</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-1.085615228166136</v>
+        <v>0.4703045771812173</v>
       </c>
       <c r="D60" t="n">
-        <v>1.085615228166136</v>
+        <v>0.4703045771812173</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1820,18 +1820,18 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AnnualIncome_Bin_1</t>
+          <t>NewCustomer_Y</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.036253139009862</v>
+        <v>-0.464755649561411</v>
       </c>
       <c r="D61" t="n">
-        <v>1.036253139009862</v>
+        <v>0.464755649561411</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1843,18 +1843,18 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AnnualIncome_Bin_4</t>
+          <t>Age_Bin_4</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.9483451721092596</v>
+        <v>-0.448470996268858</v>
       </c>
       <c r="D62" t="n">
-        <v>0.9483451721092596</v>
+        <v>0.448470996268858</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1866,18 +1866,18 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Month_Bin_4</t>
+          <t>ServiceType_N</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-0.8281111987045929</v>
+        <v>0.4344308964433812</v>
       </c>
       <c r="D63" t="n">
-        <v>0.8281111987045929</v>
+        <v>0.4344308964433812</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1893,14 +1893,14 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-0.7495061774971105</v>
+        <v>0.4093922764558039</v>
       </c>
       <c r="D64" t="n">
-        <v>0.7495061774971105</v>
+        <v>0.4093922764558039</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1912,14 +1912,14 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Year_2010</t>
+          <t>Dependents_No</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-0.7079362142599361</v>
+        <v>-0.3958404404040901</v>
       </c>
       <c r="D65" t="n">
-        <v>0.7079362142599361</v>
+        <v>0.3958404404040901</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-0.6309122041596604</v>
+        <v>-0.39301076104594</v>
       </c>
       <c r="D66" t="n">
-        <v>0.6309122041596604</v>
+        <v>0.39301076104594</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -1958,14 +1958,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ServiceType_H</t>
+          <t>Market_Southeast</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-0.6149378278800016</v>
+        <v>-0.3663527287111104</v>
       </c>
       <c r="D67" t="n">
-        <v>0.6149378278800016</v>
+        <v>0.3663527287111104</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -1981,18 +1981,18 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Month_Bin_2</t>
+          <t>AnnualIncome_Bin_1</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-0.5624976924991137</v>
+        <v>0.3539349424582461</v>
       </c>
       <c r="D68" t="n">
-        <v>0.5624976924991137</v>
+        <v>0.3539349424582461</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -2004,14 +2004,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NewCustomer_Y</t>
+          <t>Market_Southwest</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-0.5565085936722874</v>
+        <v>-0.3490538039740028</v>
       </c>
       <c r="D69" t="n">
-        <v>0.5565085936722874</v>
+        <v>0.3490538039740028</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2027,14 +2027,14 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Age_Bin_3</t>
+          <t>PaymentMethod_Gov</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.5503553950450033</v>
+        <v>0.3357368858597048</v>
       </c>
       <c r="D70" t="n">
-        <v>0.5503553950450033</v>
+        <v>0.3357368858597048</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2050,18 +2050,18 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Market_Southeast</t>
+          <t>Classification2_3</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-0.5262323028111707</v>
+        <v>0.3087928070096965</v>
       </c>
       <c r="D71" t="n">
-        <v>0.5262323028111707</v>
+        <v>0.3087928070096965</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -2073,18 +2073,18 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ServiceType_I</t>
+          <t>Age_Bin_2</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-0.4945073323128534</v>
+        <v>0.3016733875307003</v>
       </c>
       <c r="D72" t="n">
-        <v>0.4945073323128534</v>
+        <v>0.3016733875307003</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Market_Southwest</t>
+          <t>Market_Northeast</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-0.4854318122174772</v>
+        <v>-0.2838586838038293</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4854318122174772</v>
+        <v>0.2838586838038293</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2119,18 +2119,18 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ServiceType_N</t>
+          <t>ServiceType_I</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.4590640832100003</v>
+        <v>-0.280477060259903</v>
       </c>
       <c r="D74" t="n">
-        <v>0.4590640832100003</v>
+        <v>0.280477060259903</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -2142,18 +2142,18 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Age_Bin_4</t>
+          <t>Market_Midwest</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.4510175921697575</v>
+        <v>-0.271131029484952</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4510175921697575</v>
+        <v>0.271131029484952</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -2165,18 +2165,18 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AnnualIncome_Bin_2</t>
+          <t>ServiceType_C</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.3970566090190771</v>
+        <v>-0.2435532468740588</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3970566090190771</v>
+        <v>0.2435532468740588</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -2188,14 +2188,14 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Market_Midwest</t>
+          <t>Classification1_1</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-0.3799378073345281</v>
+        <v>-0.172309652366481</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3799378073345281</v>
+        <v>0.172309652366481</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2211,18 +2211,18 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Market_Northeast</t>
+          <t>Age_Bin_1</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-0.3535948361115366</v>
+        <v>0.1665791801599488</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3535948361115366</v>
+        <v>0.1665791801599488</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dependents_Yes</t>
+          <t>Classification1_4</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-0.3416727746815555</v>
+        <v>-0.1646947211444467</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3416727746815555</v>
+        <v>0.1646947211444467</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2257,14 +2257,14 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Credit_Bin_1</t>
+          <t>Government_Y</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-0.3381450805284534</v>
+        <v>-0.1588431981858257</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3381450805284534</v>
+        <v>0.1588431981858257</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2280,14 +2280,14 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Age_Bin_2</t>
+          <t>Market_Western</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.3301706597060556</v>
+        <v>0.15751270793909</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3301706597060556</v>
+        <v>0.15751270793909</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2303,14 +2303,14 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Government_Y</t>
+          <t>Classification1_2</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-0.3276384509147675</v>
+        <v>-0.1383191710526028</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3276384509147675</v>
+        <v>0.1383191710526028</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2326,18 +2326,18 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ServiceType_C</t>
+          <t>PaymentMethod_Other</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-0.2954903434101237</v>
+        <v>0.1209719440855333</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2954903434101237</v>
+        <v>0.1209719440855333</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -2349,14 +2349,14 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ServiceType_S</t>
+          <t>Classification2_4</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-0.263530142911565</v>
+        <v>-0.1177867295761607</v>
       </c>
       <c r="D84" t="n">
-        <v>0.263530142911565</v>
+        <v>0.1177867295761607</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2372,18 +2372,18 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Credit_Bin_4</t>
+          <t>Classification1_3</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.2239256257971113</v>
+        <v>-0.1177768014934094</v>
       </c>
       <c r="D85" t="n">
-        <v>0.2239256257971113</v>
+        <v>0.1177768014934094</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -2395,14 +2395,14 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MaritalStatus_Separ</t>
+          <t>ServiceType_S</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-0.2004763768654884</v>
+        <v>-0.1092746225317039</v>
       </c>
       <c r="D86" t="n">
-        <v>0.2004763768654884</v>
+        <v>0.1092746225317039</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2418,18 +2418,18 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Market_Western</t>
+          <t>Gender_M</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.1988142579665853</v>
+        <v>-0.07675441687149499</v>
       </c>
       <c r="D87" t="n">
-        <v>0.1988142579665853</v>
+        <v>0.07675441687149499</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -2441,18 +2441,18 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Month_Bin_1</t>
+          <t>Classification2_1</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-0.1913056887944666</v>
+        <v>0.07340951970324866</v>
       </c>
       <c r="D88" t="n">
-        <v>0.1913056887944666</v>
+        <v>0.07340951970324866</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -2464,18 +2464,18 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Classification1_1</t>
+          <t>Classification2_2</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-0.186106253636505</v>
+        <v>0.07157642099835235</v>
       </c>
       <c r="D89" t="n">
-        <v>0.186106253636505</v>
+        <v>0.07157642099835235</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -2487,18 +2487,18 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PaymentMethod_Gov</t>
+          <t>PaymentMethod_Direct</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.185527643416262</v>
+        <v>-0.06591822051081991</v>
       </c>
       <c r="D90" t="n">
-        <v>0.185527643416262</v>
+        <v>0.06591822051081991</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -2510,18 +2510,18 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Classification2_3</t>
+          <t>Credit_Bin_2</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.1756027549588279</v>
+        <v>-0.05584343904140666</v>
       </c>
       <c r="D91" t="n">
-        <v>0.1756027549588279</v>
+        <v>0.05584343904140666</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -2533,340 +2533,18 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Classification1_2</t>
+          <t>Market_MountainPlains</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-0.1744908698008987</v>
+        <v>0.01778127001555822</v>
       </c>
       <c r="D92" t="n">
-        <v>0.1744908698008987</v>
+        <v>0.01778127001555822</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Classification2_4</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.1521464232705724</v>
-      </c>
-      <c r="D93" t="n">
-        <v>0.1521464232705724</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Age_Bin_1</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>0.1408148100368552</v>
-      </c>
-      <c r="D94" t="n">
-        <v>0.1408148100368552</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Classification1_4</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>-0.1406806555186657</v>
-      </c>
-      <c r="D95" t="n">
-        <v>0.1406806555186657</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Classification1_3</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>-0.1225989111895158</v>
-      </c>
-      <c r="D96" t="n">
-        <v>0.1225989111895158</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>MaritalStatus_Single</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>-0.0987497998264983</v>
-      </c>
-      <c r="D97" t="n">
-        <v>0.0987497998264983</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>MaritalStatus_Married</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>0.09781459407990593</v>
-      </c>
-      <c r="D98" t="n">
-        <v>0.09781459407990593</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>PaymentMethod_Direct</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>0.07701412842716285</v>
-      </c>
-      <c r="D99" t="n">
-        <v>0.07701412842716285</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>PaymentMethod_Other</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.06645466405520097</v>
-      </c>
-      <c r="D100" t="n">
-        <v>0.06645466405520097</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Dependents_No</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.06612505376619687</v>
-      </c>
-      <c r="D101" t="n">
-        <v>0.06612505376619687</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Classification2_2</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>0.05802469786345175</v>
-      </c>
-      <c r="D102" t="n">
-        <v>0.05802469786345175</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Gender_M</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.04716836210611199</v>
-      </c>
-      <c r="D103" t="n">
-        <v>0.04716836210611199</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Credit_Bin_2</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.04614148585920085</v>
-      </c>
-      <c r="D104" t="n">
-        <v>0.04614148585920085</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Market_MountainPlains</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>0.0213362041045462</v>
-      </c>
-      <c r="D105" t="n">
-        <v>0.0213362041045462</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Low Group</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Classification2_1</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>-0.01472211212959493</v>
-      </c>
-      <c r="D106" t="n">
-        <v>0.01472211212959493</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
